--- a/public/consignmentapp_SampleDATA/upload_annexure.xlsx
+++ b/public/consignmentapp_SampleDATA/upload_annexure.xlsx
@@ -88,6 +88,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0;[Red]0"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -130,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -153,11 +156,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -189,6 +203,21 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,7 +524,8 @@
   <cols>
     <col min="1" max="1" width="21.08984375" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="12"/>
+    <col min="8" max="8" width="9.453125" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.36328125" customWidth="1"/>
     <col min="11" max="13" width="17.90625" customWidth="1"/>
@@ -508,7 +538,7 @@
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -523,7 +553,7 @@
       <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -564,12 +594,14 @@
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="15">
+        <v>1000</v>
+      </c>
       <c r="D2" s="8">
-        <v>42478</v>
-      </c>
-      <c r="E2" s="5">
-        <v>100</v>
+        <v>46130</v>
+      </c>
+      <c r="E2" s="7">
+        <v>46134</v>
       </c>
       <c r="F2" s="5">
         <v>200</v>
@@ -577,17 +609,17 @@
       <c r="G2" s="6">
         <v>1200</v>
       </c>
-      <c r="H2" s="9">
-        <v>46131</v>
+      <c r="H2" s="11">
+        <v>100</v>
       </c>
       <c r="I2" s="9">
         <v>46134</v>
       </c>
-      <c r="J2" s="6">
-        <v>7</v>
+      <c r="J2" s="9">
+        <v>46138</v>
       </c>
       <c r="K2" s="4">
-        <v>1234</v>
+        <v>6</v>
       </c>
       <c r="L2" s="4">
         <v>1000</v>
@@ -606,6 +638,9 @@
       </c>
       <c r="Q2" s="6">
         <v>250</v>
+      </c>
+      <c r="R2" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
@@ -615,12 +650,14 @@
       <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="15">
+        <v>1000</v>
+      </c>
       <c r="D3" s="8">
-        <v>42482</v>
-      </c>
-      <c r="E3" s="5">
-        <v>100</v>
+        <v>46134</v>
+      </c>
+      <c r="E3" s="7">
+        <v>46137</v>
       </c>
       <c r="F3" s="5">
         <v>200</v>
@@ -628,17 +665,17 @@
       <c r="G3" s="6">
         <v>1200</v>
       </c>
-      <c r="H3" s="9">
-        <v>46134</v>
+      <c r="H3" s="11">
+        <v>100</v>
       </c>
       <c r="I3" s="9">
         <v>46141</v>
       </c>
-      <c r="J3" s="6">
-        <v>8</v>
+      <c r="J3" s="9">
+        <v>46142</v>
       </c>
       <c r="K3" s="4">
-        <v>1234</v>
+        <v>5</v>
       </c>
       <c r="L3" s="4">
         <v>5000</v>
@@ -657,6 +694,9 @@
       </c>
       <c r="Q3" s="6">
         <v>250</v>
+      </c>
+      <c r="R3" s="13">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
